--- a/docs/formatos/cronograma-prestamo.xlsx
+++ b/docs/formatos/cronograma-prestamo.xlsx
@@ -1138,7 +1138,7 @@
         <v>22</v>
       </c>
       <c r="B16" s="9">
-        <f>IF(N(B15)&gt;0,ROUND(B14/B15,2),0)</f>
+        <f>IF(N(B15)&gt;0,ROUNDUP(B14/B15,2),0)</f>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
@@ -2221,7 +2221,7 @@
         <v>22</v>
       </c>
       <c r="B16" s="9">
-        <f>IF(N(B15)&gt;0,ROUND(B14/B15,2),0)</f>
+        <f>IF(N(B15)&gt;0,ROUNDUP(B14/B15,2),0)</f>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
